--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -8895,7 +8895,7 @@
         <v>119013583</v>
       </c>
       <c r="B79" t="n">
-        <v>57308</v>
+        <v>57384</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9016,6 +9016,823 @@
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>124801653</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>554970</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6954058</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>124801657</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>554914</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6954151</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>124801645</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>554946</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6953955</v>
+      </c>
+      <c r="S82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>124801644</v>
+      </c>
+      <c r="B83" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>555209</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6953983</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>124801651</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57624</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>554989</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6954003</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>124801648</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>555153</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6954003</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>124801658</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>lokmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>554914</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6954151</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9140,10 +9140,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801657</v>
+        <v>124801651</v>
       </c>
       <c r="B81" t="n">
-        <v>57883</v>
+        <v>57624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9156,16 +9156,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9173,10 +9173,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9185,10 +9189,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554914</v>
+        <v>554989</v>
       </c>
       <c r="R81" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9220,7 +9224,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9230,7 +9234,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9257,10 +9261,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801645</v>
+        <v>124801644</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9269,35 +9273,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9306,13 +9306,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554946</v>
+        <v>555209</v>
       </c>
       <c r="R82" t="n">
-        <v>6953955</v>
+        <v>6953983</v>
       </c>
       <c r="S82" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9339,19 +9339,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>07:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9378,10 +9368,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801644</v>
+        <v>124801657</v>
       </c>
       <c r="B83" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9394,27 +9384,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9423,10 +9413,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555209</v>
+        <v>554914</v>
       </c>
       <c r="R83" t="n">
-        <v>6953983</v>
+        <v>6954151</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9456,9 +9446,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9485,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801651</v>
+        <v>124801648</v>
       </c>
       <c r="B84" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9497,20 +9497,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9518,14 +9518,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9534,7 +9530,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>554989</v>
+        <v>555153</v>
       </c>
       <c r="R84" t="n">
         <v>6954003</v>
@@ -9567,19 +9563,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>06:50</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9606,10 +9597,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801648</v>
+        <v>124801658</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9622,27 +9613,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9651,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555153</v>
+        <v>554914</v>
       </c>
       <c r="R85" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9684,14 +9675,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9718,10 +9714,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124801658</v>
+        <v>124801645</v>
       </c>
       <c r="B86" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9734,24 +9730,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>554914</v>
+        <v>554946</v>
       </c>
       <c r="R86" t="n">
-        <v>6954151</v>
+        <v>6953955</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9140,10 +9140,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801651</v>
+        <v>124801645</v>
       </c>
       <c r="B81" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9152,20 +9152,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9189,13 +9189,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554989</v>
+        <v>554946</v>
       </c>
       <c r="R81" t="n">
-        <v>6954003</v>
+        <v>6953955</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9261,10 +9261,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801644</v>
+        <v>124801658</v>
       </c>
       <c r="B82" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9273,31 +9273,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555209</v>
+        <v>554914</v>
       </c>
       <c r="R82" t="n">
-        <v>6953983</v>
+        <v>6954151</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9339,9 +9339,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9368,10 +9378,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801657</v>
+        <v>124801648</v>
       </c>
       <c r="B83" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9380,20 +9390,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9404,7 +9414,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9413,10 +9423,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554914</v>
+        <v>555153</v>
       </c>
       <c r="R83" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9446,19 +9456,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9485,10 +9490,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801648</v>
+        <v>124801651</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>57624</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9497,20 +9502,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9518,10 +9523,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9530,7 +9539,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555153</v>
+        <v>554989</v>
       </c>
       <c r="R84" t="n">
         <v>6954003</v>
@@ -9563,14 +9572,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9597,10 +9611,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801658</v>
+        <v>124801657</v>
       </c>
       <c r="B85" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,25 +9623,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9714,10 +9728,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124801645</v>
+        <v>124801644</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9726,35 +9740,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9763,13 +9773,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>554946</v>
+        <v>555209</v>
       </c>
       <c r="R86" t="n">
-        <v>6953955</v>
+        <v>6953983</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9796,19 +9806,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>07:00</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9140,47 +9140,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801645</v>
+        <v>124801644</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9189,13 +9185,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554946</v>
+        <v>555209</v>
       </c>
       <c r="R81" t="n">
-        <v>6953955</v>
+        <v>6953983</v>
       </c>
       <c r="S81" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9222,19 +9218,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>07:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9728,43 +9714,47 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124801644</v>
+        <v>124801645</v>
       </c>
       <c r="B86" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9773,13 +9763,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555209</v>
+        <v>554946</v>
       </c>
       <c r="R86" t="n">
-        <v>6953983</v>
+        <v>6953955</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9806,9 +9796,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801653</v>
+        <v>124801657</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9054,7 +9054,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554970</v>
+        <v>554914</v>
       </c>
       <c r="R80" t="n">
-        <v>6954058</v>
+        <v>6954151</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9108,12 +9108,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9140,10 +9135,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801644</v>
+        <v>124801658</v>
       </c>
       <c r="B81" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9152,31 +9147,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9185,10 +9180,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555209</v>
+        <v>554914</v>
       </c>
       <c r="R81" t="n">
-        <v>6953983</v>
+        <v>6954151</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9218,9 +9213,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9247,10 +9252,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801658</v>
+        <v>124801651</v>
       </c>
       <c r="B82" t="n">
-        <v>57666</v>
+        <v>57624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9259,31 +9264,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9292,10 +9301,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554914</v>
+        <v>554989</v>
       </c>
       <c r="R82" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9327,7 +9336,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9337,7 +9346,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9364,7 +9373,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801648</v>
+        <v>124801653</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -9409,10 +9418,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555153</v>
+        <v>554970</v>
       </c>
       <c r="R83" t="n">
-        <v>6954003</v>
+        <v>6954058</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9442,14 +9451,24 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>många färska bark</t>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9476,10 +9495,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801651</v>
+        <v>124801648</v>
       </c>
       <c r="B84" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9488,20 +9507,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9509,14 +9528,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9525,7 +9540,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>554989</v>
+        <v>555153</v>
       </c>
       <c r="R84" t="n">
         <v>6954003</v>
@@ -9558,19 +9573,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>06:50</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9597,10 +9607,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801657</v>
+        <v>124801644</v>
       </c>
       <c r="B85" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9613,27 +9623,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9642,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554914</v>
+        <v>555209</v>
       </c>
       <c r="R85" t="n">
-        <v>6954151</v>
+        <v>6953983</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9675,19 +9685,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>06:00</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801657</v>
+        <v>124801651</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>57624</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9034,16 +9034,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9051,10 +9051,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9067,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554914</v>
+        <v>554989</v>
       </c>
       <c r="R80" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9098,7 +9102,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9108,7 +9112,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9252,10 +9256,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801651</v>
+        <v>124801657</v>
       </c>
       <c r="B82" t="n">
-        <v>57624</v>
+        <v>57883</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9268,16 +9272,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9285,14 +9289,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554989</v>
+        <v>554914</v>
       </c>
       <c r="R82" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9373,7 +9373,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801653</v>
+        <v>124801648</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -9418,10 +9418,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554970</v>
+        <v>555153</v>
       </c>
       <c r="R83" t="n">
-        <v>6954058</v>
+        <v>6954003</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9451,24 +9451,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9495,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801648</v>
+        <v>124801644</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9507,25 +9497,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9540,10 +9530,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555153</v>
+        <v>555209</v>
       </c>
       <c r="R84" t="n">
-        <v>6954003</v>
+        <v>6953983</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9576,11 +9566,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,10 +9592,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801644</v>
+        <v>124801653</v>
       </c>
       <c r="B85" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9619,25 +9604,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9652,10 +9637,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555209</v>
+        <v>554970</v>
       </c>
       <c r="R85" t="n">
-        <v>6953983</v>
+        <v>6954058</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9685,9 +9670,24 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801651</v>
+        <v>124801644</v>
       </c>
       <c r="B80" t="n">
-        <v>57624</v>
+        <v>56722</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9034,31 +9034,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9067,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554989</v>
+        <v>555209</v>
       </c>
       <c r="R80" t="n">
-        <v>6954003</v>
+        <v>6953983</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9100,19 +9096,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>06:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9485,10 +9471,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801644</v>
+        <v>124801651</v>
       </c>
       <c r="B84" t="n">
-        <v>56722</v>
+        <v>57624</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9501,27 +9487,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9530,10 +9520,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555209</v>
+        <v>554989</v>
       </c>
       <c r="R84" t="n">
-        <v>6953983</v>
+        <v>6954003</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9563,9 +9553,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801644</v>
+        <v>124801653</v>
       </c>
       <c r="B80" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,25 +9030,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555209</v>
+        <v>554970</v>
       </c>
       <c r="R80" t="n">
-        <v>6953983</v>
+        <v>6954058</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9096,9 +9096,24 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9125,10 +9140,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801658</v>
+        <v>124801657</v>
       </c>
       <c r="B81" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9137,25 +9152,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9242,10 +9257,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801657</v>
+        <v>124801644</v>
       </c>
       <c r="B82" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9258,27 +9273,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9287,10 +9302,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554914</v>
+        <v>555209</v>
       </c>
       <c r="R82" t="n">
-        <v>6954151</v>
+        <v>6953983</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9320,19 +9335,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9359,10 +9364,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801648</v>
+        <v>124801651</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>57624</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9371,20 +9376,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9392,10 +9397,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9404,7 +9413,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555153</v>
+        <v>554989</v>
       </c>
       <c r="R83" t="n">
         <v>6954003</v>
@@ -9437,14 +9446,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9471,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801651</v>
+        <v>124801648</v>
       </c>
       <c r="B84" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9483,20 +9497,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9504,14 +9518,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9520,7 +9530,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>554989</v>
+        <v>555153</v>
       </c>
       <c r="R84" t="n">
         <v>6954003</v>
@@ -9553,19 +9563,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>06:50</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9592,10 +9597,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801653</v>
+        <v>124801658</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9608,27 +9613,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9637,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554970</v>
+        <v>554914</v>
       </c>
       <c r="R85" t="n">
-        <v>6954058</v>
+        <v>6954151</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9672,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9682,12 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801653</v>
+        <v>124801657</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9054,7 +9054,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554970</v>
+        <v>554914</v>
       </c>
       <c r="R80" t="n">
-        <v>6954058</v>
+        <v>6954151</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9108,12 +9108,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9140,10 +9135,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801657</v>
+        <v>124801653</v>
       </c>
       <c r="B81" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9152,20 +9147,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9176,7 +9171,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9185,10 +9180,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554914</v>
+        <v>554970</v>
       </c>
       <c r="R81" t="n">
-        <v>6954151</v>
+        <v>6954058</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9220,7 +9215,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9230,7 +9225,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9257,10 +9257,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801644</v>
+        <v>124801651</v>
       </c>
       <c r="B82" t="n">
-        <v>56722</v>
+        <v>57624</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9273,27 +9273,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9302,10 +9306,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555209</v>
+        <v>554989</v>
       </c>
       <c r="R82" t="n">
-        <v>6953983</v>
+        <v>6954003</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9335,9 +9339,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9364,10 +9378,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801651</v>
+        <v>124801644</v>
       </c>
       <c r="B83" t="n">
-        <v>57624</v>
+        <v>56722</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9380,31 +9394,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9413,10 +9423,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554989</v>
+        <v>555209</v>
       </c>
       <c r="R83" t="n">
-        <v>6954003</v>
+        <v>6953983</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9446,19 +9456,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>06:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9485,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801648</v>
+        <v>124801658</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9501,27 +9501,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555153</v>
+        <v>554914</v>
       </c>
       <c r="R84" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9563,14 +9563,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9597,10 +9602,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801658</v>
+        <v>124801648</v>
       </c>
       <c r="B85" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9613,27 +9618,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9642,10 +9647,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554914</v>
+        <v>555153</v>
       </c>
       <c r="R85" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9675,19 +9680,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801657</v>
+        <v>124801648</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9054,7 +9054,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554914</v>
+        <v>555153</v>
       </c>
       <c r="R80" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9096,19 +9096,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9257,10 +9252,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801651</v>
+        <v>124801657</v>
       </c>
       <c r="B82" t="n">
-        <v>57624</v>
+        <v>57883</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9273,16 +9268,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9290,14 +9285,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9306,10 +9297,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554989</v>
+        <v>554914</v>
       </c>
       <c r="R82" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9341,7 +9332,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9351,7 +9342,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9602,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801648</v>
+        <v>124801651</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>57624</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9614,20 +9605,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9635,10 +9626,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9647,7 +9642,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555153</v>
+        <v>554989</v>
       </c>
       <c r="R85" t="n">
         <v>6954003</v>
@@ -9680,14 +9675,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801648</v>
+        <v>124801658</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9034,27 +9034,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555153</v>
+        <v>554914</v>
       </c>
       <c r="R80" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9096,14 +9096,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9130,10 +9135,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801653</v>
+        <v>124801644</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9142,25 +9147,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9175,10 +9180,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554970</v>
+        <v>555209</v>
       </c>
       <c r="R81" t="n">
-        <v>6954058</v>
+        <v>6953983</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9208,24 +9213,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9252,10 +9242,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801657</v>
+        <v>124801653</v>
       </c>
       <c r="B82" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9264,20 +9254,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9288,7 +9278,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9297,10 +9287,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554914</v>
+        <v>554970</v>
       </c>
       <c r="R82" t="n">
-        <v>6954151</v>
+        <v>6954058</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9332,7 +9322,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9342,7 +9332,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9369,10 +9364,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801644</v>
+        <v>124801651</v>
       </c>
       <c r="B83" t="n">
-        <v>56722</v>
+        <v>57624</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9385,27 +9380,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9414,10 +9413,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555209</v>
+        <v>554989</v>
       </c>
       <c r="R83" t="n">
-        <v>6953983</v>
+        <v>6954003</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9447,9 +9446,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9476,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801658</v>
+        <v>124801648</v>
       </c>
       <c r="B84" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9492,27 +9501,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9521,10 +9530,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>554914</v>
+        <v>555153</v>
       </c>
       <c r="R84" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9554,19 +9563,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,10 +9597,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801651</v>
+        <v>124801657</v>
       </c>
       <c r="B85" t="n">
-        <v>57624</v>
+        <v>57883</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9609,16 +9613,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9626,14 +9630,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554989</v>
+        <v>554914</v>
       </c>
       <c r="R85" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801658</v>
+        <v>124801648</v>
       </c>
       <c r="B80" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9034,27 +9034,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554914</v>
+        <v>555153</v>
       </c>
       <c r="R80" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9096,19 +9096,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>06:00</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9242,10 +9237,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801653</v>
+        <v>124801658</v>
       </c>
       <c r="B82" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9258,27 +9253,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9287,10 +9282,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554970</v>
+        <v>554914</v>
       </c>
       <c r="R82" t="n">
-        <v>6954058</v>
+        <v>6954151</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9322,7 +9317,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9332,12 +9327,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9364,10 +9354,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801651</v>
+        <v>124801653</v>
       </c>
       <c r="B83" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9376,20 +9366,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9397,14 +9387,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9413,10 +9399,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554989</v>
+        <v>554970</v>
       </c>
       <c r="R83" t="n">
-        <v>6954003</v>
+        <v>6954058</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9448,7 +9434,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9458,7 +9444,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9485,10 +9476,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801648</v>
+        <v>124801657</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9497,20 +9488,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9521,7 +9512,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9530,10 +9521,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555153</v>
+        <v>554914</v>
       </c>
       <c r="R84" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9563,14 +9554,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9597,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801657</v>
+        <v>124801651</v>
       </c>
       <c r="B85" t="n">
-        <v>57883</v>
+        <v>57624</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9613,16 +9609,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9630,10 +9626,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554914</v>
+        <v>554989</v>
       </c>
       <c r="R85" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9130,10 +9130,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801644</v>
+        <v>124801658</v>
       </c>
       <c r="B81" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9142,31 +9142,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555209</v>
+        <v>554914</v>
       </c>
       <c r="R81" t="n">
-        <v>6953983</v>
+        <v>6954151</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9208,9 +9208,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9237,10 +9247,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801658</v>
+        <v>124801644</v>
       </c>
       <c r="B82" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9249,31 +9259,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9282,10 +9292,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554914</v>
+        <v>555209</v>
       </c>
       <c r="R82" t="n">
-        <v>6954151</v>
+        <v>6953983</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9315,19 +9325,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801648</v>
+        <v>124801657</v>
       </c>
       <c r="B80" t="n">
-        <v>57513</v>
+        <v>58001</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,20 +9030,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9054,7 +9054,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555153</v>
+        <v>554914</v>
       </c>
       <c r="R80" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9096,14 +9096,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9130,10 +9135,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801658</v>
+        <v>124801651</v>
       </c>
       <c r="B81" t="n">
-        <v>57666</v>
+        <v>57738</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9142,31 +9147,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9175,10 +9184,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554914</v>
+        <v>554989</v>
       </c>
       <c r="R81" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9210,7 +9219,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9220,7 +9229,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9247,10 +9256,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801644</v>
+        <v>124801648</v>
       </c>
       <c r="B82" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9259,25 +9268,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9292,10 +9301,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555209</v>
+        <v>555153</v>
       </c>
       <c r="R82" t="n">
-        <v>6953983</v>
+        <v>6954003</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9328,6 +9337,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9354,10 +9368,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801653</v>
+        <v>124801658</v>
       </c>
       <c r="B83" t="n">
-        <v>57513</v>
+        <v>57793</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9370,27 +9384,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9399,10 +9413,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554970</v>
+        <v>554914</v>
       </c>
       <c r="R83" t="n">
-        <v>6954058</v>
+        <v>6954151</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9434,7 +9448,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9444,12 +9458,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9476,10 +9485,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801657</v>
+        <v>124801644</v>
       </c>
       <c r="B84" t="n">
-        <v>57883</v>
+        <v>56836</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9492,27 +9501,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9521,10 +9530,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>554914</v>
+        <v>555209</v>
       </c>
       <c r="R84" t="n">
-        <v>6954151</v>
+        <v>6953983</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9554,19 +9563,9 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>06:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9593,10 +9592,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801651</v>
+        <v>124801653</v>
       </c>
       <c r="B85" t="n">
-        <v>57624</v>
+        <v>57635</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9605,20 +9604,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9626,14 +9625,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9642,10 +9637,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554989</v>
+        <v>554970</v>
       </c>
       <c r="R85" t="n">
-        <v>6954003</v>
+        <v>6954058</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9677,7 +9672,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9687,7 +9682,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9717,7 +9717,7 @@
         <v>124801645</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9018,10 +9018,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801657</v>
+        <v>124801658</v>
       </c>
       <c r="B80" t="n">
-        <v>58001</v>
+        <v>57793</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,25 +9030,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9135,10 +9135,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801651</v>
+        <v>124801653</v>
       </c>
       <c r="B81" t="n">
-        <v>57738</v>
+        <v>57635</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9147,20 +9147,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9168,14 +9168,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9184,10 +9180,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554989</v>
+        <v>554970</v>
       </c>
       <c r="R81" t="n">
-        <v>6954003</v>
+        <v>6954058</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9219,7 +9215,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9229,7 +9225,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9256,10 +9257,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801648</v>
+        <v>124801657</v>
       </c>
       <c r="B82" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9268,20 +9269,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9292,7 +9293,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9301,10 +9302,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555153</v>
+        <v>554914</v>
       </c>
       <c r="R82" t="n">
-        <v>6954003</v>
+        <v>6954151</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9334,14 +9335,19 @@
           <t>2025-04-02</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9368,10 +9374,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801658</v>
+        <v>124801651</v>
       </c>
       <c r="B83" t="n">
-        <v>57793</v>
+        <v>57738</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9380,31 +9386,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9413,10 +9423,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554914</v>
+        <v>554989</v>
       </c>
       <c r="R83" t="n">
-        <v>6954151</v>
+        <v>6954003</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9448,7 +9458,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9458,7 +9468,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9592,7 +9602,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801653</v>
+        <v>124801648</v>
       </c>
       <c r="B85" t="n">
         <v>57635</v>
@@ -9637,10 +9647,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>554970</v>
+        <v>555153</v>
       </c>
       <c r="R85" t="n">
-        <v>6954058</v>
+        <v>6954003</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9670,24 +9680,14 @@
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>färska barkfläk</t>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -9719,11 +9719,6 @@
       <c r="B86" t="n">
         <v>57635</v>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790285</v>
+        <v>96790279</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555216.4584501918</v>
+        <v>554950</v>
       </c>
       <c r="R2" t="n">
-        <v>6953886.768271047</v>
+        <v>6953774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>tät, drygt 100-årig barrskog</t>
+          <t>äldre granskog med torrträd</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # äldre sälg</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790283</v>
+        <v>96790280</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555216.4584501918</v>
+        <v>554917</v>
       </c>
       <c r="R3" t="n">
-        <v>6953886.768271047</v>
+        <v>6953780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,21 +857,11 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,15 +873,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>tät, drygt 100-årig barrskog</t>
+          <t>äldre granskog med torrträd</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # äldre sälg</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790267</v>
+        <v>119013554</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,34 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555438.1857016436</v>
+        <v>555162</v>
       </c>
       <c r="R4" t="n">
-        <v>6954202.552732978</v>
+        <v>6953756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,48 +984,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>gammal grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov granlåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96790268</v>
+        <v>119013555</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,14 +1031,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555383.361053368</v>
+        <v>555253</v>
       </c>
       <c r="R5" t="n">
-        <v>6954210.809208116</v>
+        <v>6953747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,22 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,70 +1081,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>ljusare fuktdråg i gammal grannaturskog</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal sälg</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96790281</v>
+        <v>96790277</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1231,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554952.1986868125</v>
+        <v>555008</v>
       </c>
       <c r="R6" t="n">
-        <v>6953831.411112087</v>
+        <v>6953770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1264,21 +1165,11 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1290,15 +1181,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>tät, drygt 100-årig barrskog med aspinslag</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+          <t>vid källmiljö i olikåldrig, naturskogsartad  granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,37 +1203,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96790269</v>
+        <v>96790278</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555383.361053368</v>
+        <v>555002</v>
       </c>
       <c r="R7" t="n">
-        <v>6954210.809208116</v>
+        <v>6953764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1393,21 +1271,11 @@
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1419,7 +1287,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>ljusare fuktdråg i gammal grannaturskog</t>
+          <t>olikåldrig, naturskogsartad  granskog med hänglav</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1427,7 +1295,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1449,50 +1317,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96790274</v>
+        <v>119013562</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555166.2434597021</v>
+        <v>554814</v>
       </c>
       <c r="R8" t="n">
-        <v>6953976.337403046</v>
+        <v>6953758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,22 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera m2 med endast bladrosetter, uppskattar 2000 bladrosetter och 10 blomställningar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,50 +1405,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre, naturskogsartad  granskog med hänglav</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>1 substratenheter # barklös, grov granlåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96790282</v>
+        <v>119013563</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,17 +1452,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555225.3249022372</v>
+        <v>554835</v>
       </c>
       <c r="R9" t="n">
-        <v>6953906.192126275</v>
+        <v>6953776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,22 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1672,85 +1507,68 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>tät, drygt 100-årig barrskog</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96790286</v>
+        <v>119013565</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lokmyrhöjdens västsida, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554896.901319666</v>
+        <v>555098</v>
       </c>
       <c r="R10" t="n">
-        <v>6954005.802271655</v>
+        <v>6953757</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1777,22 +1595,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>300 badrosetter 3 blomställningar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,85 +1614,68 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>gallrad, drygt 100-årig lövrik barrskog</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>4 substratenheter # äldre asp och sälg</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119013584</v>
+        <v>119013566</v>
       </c>
       <c r="B11" t="n">
-        <v>79621</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554902</v>
+        <v>554825</v>
       </c>
       <c r="R11" t="n">
-        <v>6953838</v>
+        <v>6953708</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1906,12 +1702,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>300 bladrostter 3 blomställningar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,6 +1721,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1938,50 +1740,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119013579</v>
+        <v>119013568</v>
       </c>
       <c r="B12" t="n">
-        <v>97793</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555119</v>
+        <v>554894</v>
       </c>
       <c r="R12" t="n">
-        <v>6954134</v>
+        <v>6953706</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,12 +1809,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>130 bladrosetter 10 blomställningar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,6 +1828,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2040,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119013548</v>
+        <v>119013550</v>
       </c>
       <c r="B13" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554814</v>
+        <v>555259</v>
       </c>
       <c r="R13" t="n">
-        <v>6954160</v>
+        <v>6953737</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2142,15 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119013552</v>
+        <v>119013553</v>
       </c>
       <c r="B14" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555115</v>
+        <v>554843</v>
       </c>
       <c r="R14" t="n">
-        <v>6954152</v>
+        <v>6953762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,15 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119013537</v>
+        <v>119013524</v>
       </c>
       <c r="B15" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554955</v>
+        <v>554888</v>
       </c>
       <c r="R15" t="n">
-        <v>6954151</v>
+        <v>6953688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,15 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119013577</v>
+        <v>119013527</v>
       </c>
       <c r="B16" t="n">
-        <v>97793</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2386,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555002</v>
+        <v>554830</v>
       </c>
       <c r="R16" t="n">
-        <v>6954142</v>
+        <v>6953771</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,12 +2203,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,54 +2235,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119013612</v>
+        <v>119013532</v>
       </c>
       <c r="B17" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554911</v>
+        <v>555251</v>
       </c>
       <c r="R17" t="n">
-        <v>6953840</v>
+        <v>6953766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,17 +2300,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>18 bladrosetter</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,7 +2314,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2560,37 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119013530</v>
+        <v>119013582</v>
       </c>
       <c r="B18" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2600,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555091</v>
+        <v>554917</v>
       </c>
       <c r="R18" t="n">
-        <v>6954136</v>
+        <v>6954054</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,12 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,50 +2429,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119013588</v>
+        <v>96790274</v>
       </c>
       <c r="B19" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555102</v>
+        <v>555166</v>
       </c>
       <c r="R19" t="n">
-        <v>6954018</v>
+        <v>6953976</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,12 +2494,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,31 +2510,43 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>äldre, naturskogsartad  granskog med hänglav</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>1 substratenheter # barklös, grov granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119013602</v>
+        <v>96790269</v>
       </c>
       <c r="B20" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,34 +2554,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554897</v>
+        <v>555383</v>
       </c>
       <c r="R20" t="n">
-        <v>6953826</v>
+        <v>6954211</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2834,12 +2608,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,53 +2624,65 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>ljusare fuktdråg i gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119013521</v>
+        <v>119013613</v>
       </c>
       <c r="B21" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2906,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555196</v>
+        <v>555099</v>
       </c>
       <c r="R21" t="n">
-        <v>6954028</v>
+        <v>6953847</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,12 +2722,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,37 +2754,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119013559</v>
+        <v>119013614</v>
       </c>
       <c r="B22" t="n">
-        <v>97780</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3008,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554942</v>
+        <v>555092</v>
       </c>
       <c r="R22" t="n">
-        <v>6954152</v>
+        <v>6954036</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,12 +2819,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,54 +2851,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119013566</v>
+        <v>96790268</v>
       </c>
       <c r="B23" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>554825</v>
+        <v>555383</v>
       </c>
       <c r="R23" t="n">
-        <v>6953708</v>
+        <v>6954211</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3144,17 +2916,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>300 bladrostter 3 blomställningar</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,69 +2930,80 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>ljusare fuktdråg i gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal sälg</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119013558</v>
+        <v>96790285</v>
       </c>
       <c r="B24" t="n">
-        <v>97780</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555421</v>
+        <v>555216</v>
       </c>
       <c r="R24" t="n">
-        <v>6954236</v>
+        <v>6953887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,12 +3030,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3268,66 +3046,78 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>tät, drygt 100-årig barrskog</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>2 substratenheter # äldre sälg</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119013606</v>
+        <v>96790286</v>
       </c>
       <c r="B25" t="n">
-        <v>79552</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554958</v>
+        <v>554897</v>
       </c>
       <c r="R25" t="n">
-        <v>6953843</v>
+        <v>6954006</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,12 +3144,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,31 +3160,43 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>gallrad, drygt 100-årig lövrik barrskog</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>4 substratenheter # äldre asp och sälg</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119013582</v>
+        <v>119013601</v>
       </c>
       <c r="B26" t="n">
-        <v>95424</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3402,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3426,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554917</v>
+        <v>554893</v>
       </c>
       <c r="R26" t="n">
-        <v>6954054</v>
+        <v>6953947</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,54 +3290,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119013573</v>
+        <v>119013602</v>
       </c>
       <c r="B27" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555191</v>
+        <v>554897</v>
       </c>
       <c r="R27" t="n">
-        <v>6953828</v>
+        <v>6953826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,17 +3355,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 Blomma 50 bladrosetter</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3581,7 +3369,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3600,37 +3387,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119013561</v>
+        <v>119013603</v>
       </c>
       <c r="B28" t="n">
-        <v>97780</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3640,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>554826</v>
+        <v>554953</v>
       </c>
       <c r="R28" t="n">
-        <v>6954137</v>
+        <v>6953841</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3670,12 +3452,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3702,37 +3484,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119013594</v>
+        <v>119013604</v>
       </c>
       <c r="B29" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3742,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>554818</v>
+        <v>554885</v>
       </c>
       <c r="R29" t="n">
-        <v>6954164</v>
+        <v>6954036</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3804,15 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119013586</v>
+        <v>119013584</v>
       </c>
       <c r="B30" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3820,21 +3592,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3844,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>554909</v>
+        <v>554902</v>
       </c>
       <c r="R30" t="n">
-        <v>6954096</v>
+        <v>6953838</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3906,15 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119013596</v>
+        <v>119013540</v>
       </c>
       <c r="B31" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3922,21 +3689,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3946,10 +3713,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555083</v>
+        <v>554986</v>
       </c>
       <c r="R31" t="n">
-        <v>6954043</v>
+        <v>6954151</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,12 +3743,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4008,15 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119013547</v>
+        <v>119013541</v>
       </c>
       <c r="B32" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4024,21 +3786,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4048,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555032</v>
+        <v>555060</v>
       </c>
       <c r="R32" t="n">
-        <v>6954136</v>
+        <v>6954137</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4110,54 +3872,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119013563</v>
+        <v>119013542</v>
       </c>
       <c r="B33" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>554835</v>
+        <v>555090</v>
       </c>
       <c r="R33" t="n">
-        <v>6953776</v>
+        <v>6954145</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4198,7 +3951,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4217,42 +3969,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119013571</v>
+        <v>119013583</v>
       </c>
       <c r="B34" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4261,10 +4028,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555289</v>
+        <v>555004</v>
       </c>
       <c r="R34" t="n">
-        <v>6954145</v>
+        <v>6953949</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,17 +4058,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>25 bladrosetter 6 blomställningar</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4310,7 +4072,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4329,53 +4090,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119013525</v>
+        <v>124801645</v>
       </c>
       <c r="B35" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555195</v>
+        <v>554946</v>
       </c>
       <c r="R35" t="n">
-        <v>6953833</v>
+        <v>6953955</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4399,12 +4164,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4419,65 +4194,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119013523</v>
+        <v>124801648</v>
       </c>
       <c r="B36" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555402</v>
+        <v>555153</v>
       </c>
       <c r="R36" t="n">
-        <v>6954240</v>
+        <v>6954003</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4501,12 +4276,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>många färska bark</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4521,65 +4301,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119013590</v>
+        <v>124801653</v>
       </c>
       <c r="B37" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555064</v>
+        <v>554970</v>
       </c>
       <c r="R37" t="n">
-        <v>6953871</v>
+        <v>6954058</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4603,12 +4383,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>färska barkfläk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4623,27 +4418,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119013593</v>
+        <v>124801644</v>
       </c>
       <c r="B38" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4651,37 +4441,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>554896</v>
+        <v>555209</v>
       </c>
       <c r="R38" t="n">
-        <v>6953861</v>
+        <v>6953983</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4705,12 +4500,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4725,27 +4520,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119013529</v>
+        <v>124801657</v>
       </c>
       <c r="B39" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4753,37 +4543,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555390</v>
+        <v>554914</v>
       </c>
       <c r="R39" t="n">
-        <v>6954230</v>
+        <v>6954151</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4807,12 +4602,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4827,49 +4632,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119013543</v>
+        <v>119013521</v>
       </c>
       <c r="B40" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223591</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4879,10 +4679,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>554949</v>
+        <v>555196</v>
       </c>
       <c r="R40" t="n">
-        <v>6954156</v>
+        <v>6954028</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4941,57 +4741,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119013570</v>
+        <v>124801658</v>
       </c>
       <c r="B41" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555202</v>
+        <v>554914</v>
       </c>
       <c r="R41" t="n">
-        <v>6953841</v>
+        <v>6954151</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5015,12 +4811,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5029,34 +4835,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119013614</v>
+        <v>124801651</v>
       </c>
       <c r="B42" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5064,37 +4864,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>lokmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555092</v>
+        <v>554989</v>
       </c>
       <c r="R42" t="n">
-        <v>6954036</v>
+        <v>6954003</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5118,12 +4927,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5138,27 +4957,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119013595</v>
+        <v>119013575</v>
       </c>
       <c r="B43" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5166,21 +4980,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>223591</v>
+        <v>208260</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5190,10 +5004,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>554913</v>
+        <v>555256</v>
       </c>
       <c r="R43" t="n">
-        <v>6954097</v>
+        <v>6954151</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5220,12 +5034,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5252,15 +5066,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119013597</v>
+        <v>119013576</v>
       </c>
       <c r="B44" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5268,21 +5077,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5292,10 +5101,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>554986</v>
+        <v>554812</v>
       </c>
       <c r="R44" t="n">
-        <v>6954063</v>
+        <v>6954136</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5322,12 +5131,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5354,37 +5163,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119013613</v>
+        <v>119013577</v>
       </c>
       <c r="B45" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5394,10 +5198,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555099</v>
+        <v>555002</v>
       </c>
       <c r="R45" t="n">
-        <v>6953847</v>
+        <v>6954142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5456,37 +5260,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119013601</v>
+        <v>119013578</v>
       </c>
       <c r="B46" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5496,10 +5295,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>554893</v>
+        <v>554846</v>
       </c>
       <c r="R46" t="n">
-        <v>6953947</v>
+        <v>6954143</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5558,37 +5357,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119013604</v>
+        <v>119013579</v>
       </c>
       <c r="B47" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5598,10 +5392,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>554885</v>
+        <v>555119</v>
       </c>
       <c r="R47" t="n">
-        <v>6954036</v>
+        <v>6954134</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5660,37 +5454,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119013542</v>
+        <v>119013558</v>
       </c>
       <c r="B48" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220093</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5700,10 +5489,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555090</v>
+        <v>555421</v>
       </c>
       <c r="R48" t="n">
-        <v>6954145</v>
+        <v>6954236</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5762,15 +5551,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119013546</v>
+        <v>119013559</v>
       </c>
       <c r="B49" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5778,21 +5562,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>223591</v>
+        <v>220093</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5586,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555203</v>
+        <v>554942</v>
       </c>
       <c r="R49" t="n">
-        <v>6954010</v>
+        <v>6954152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,54 +5648,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119013611</v>
+        <v>119013560</v>
       </c>
       <c r="B50" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>554915</v>
+        <v>555214</v>
       </c>
       <c r="R50" t="n">
-        <v>6953952</v>
+        <v>6954043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5938,17 +5713,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>20 bladrosetter</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5957,7 +5727,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5976,15 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119013533</v>
+        <v>119013561</v>
       </c>
       <c r="B51" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5992,21 +5756,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6016,10 +5780,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555383</v>
+        <v>554826</v>
       </c>
       <c r="R51" t="n">
-        <v>6954209</v>
+        <v>6954137</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6078,15 +5842,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119013609</v>
+        <v>96790281</v>
       </c>
       <c r="B52" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6111,21 +5870,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>554901</v>
+        <v>554952</v>
       </c>
       <c r="R52" t="n">
-        <v>6954058</v>
+        <v>6953832</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6152,17 +5907,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>70 bladrosetter en blomställning</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6171,69 +5921,80 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>tät, drygt 100-årig barrskog med aspinslag</t>
+        </is>
+      </c>
+      <c r="AN52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119013598</v>
+        <v>96790282</v>
       </c>
       <c r="B53" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Eltnäs, Jmt</t>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555001</v>
+        <v>555225</v>
       </c>
       <c r="R53" t="n">
-        <v>6953846</v>
+        <v>6953906</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6260,12 +6021,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6276,66 +6037,82 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>tät, drygt 100-årig barrskog</t>
+        </is>
+      </c>
+      <c r="AN53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119013560</v>
+        <v>119013570</v>
       </c>
       <c r="B54" t="n">
-        <v>97780</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555214</v>
+        <v>555202</v>
       </c>
       <c r="R54" t="n">
-        <v>6954043</v>
+        <v>6953841</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6376,6 +6153,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6394,50 +6172,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119013603</v>
+        <v>119013571</v>
       </c>
       <c r="B55" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>554953</v>
+        <v>555289</v>
       </c>
       <c r="R55" t="n">
-        <v>6953841</v>
+        <v>6954145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6464,12 +6241,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>25 bladrosetter 6 blomställningar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6478,6 +6260,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6496,50 +6279,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119013575</v>
+        <v>119013573</v>
       </c>
       <c r="B56" t="n">
-        <v>56290</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>208260</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555256</v>
+        <v>555191</v>
       </c>
       <c r="R56" t="n">
-        <v>6954151</v>
+        <v>6953828</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6574,12 +6356,18 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1 Blomma 50 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6598,50 +6386,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119013526</v>
+        <v>119013581</v>
       </c>
       <c r="B57" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555407</v>
+        <v>555306</v>
       </c>
       <c r="R57" t="n">
-        <v>6954244</v>
+        <v>6954137</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6668,12 +6455,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>200 bladrosetter 8 blomställningar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6682,6 +6474,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6700,50 +6493,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119013599</v>
+        <v>119013607</v>
       </c>
       <c r="B58" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>554908</v>
+        <v>555004</v>
       </c>
       <c r="R58" t="n">
-        <v>6953845</v>
+        <v>6953947</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6778,12 +6570,18 @@
           <t>2024-07-01</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>500 bladrosetter 20 blomställningar</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6802,15 +6600,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119013562</v>
+        <v>119013608</v>
       </c>
       <c r="B59" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6837,7 +6630,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6846,10 +6639,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>554814</v>
+        <v>555081</v>
       </c>
       <c r="R59" t="n">
-        <v>6953758</v>
+        <v>6953860</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6876,17 +6669,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Flera m2 med endast bladrosetter, uppskattar 2000 bladrosetter och 10 blomställningar</t>
+          <t>200 bladrosetter 11 blomställningar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,50 +6707,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119013549</v>
+        <v>119013609</v>
       </c>
       <c r="B60" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555196</v>
+        <v>554901</v>
       </c>
       <c r="R60" t="n">
-        <v>6954028</v>
+        <v>6954058</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6984,12 +6776,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>70 bladrosetter en blomställning</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6998,6 +6795,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7016,50 +6814,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119013538</v>
+        <v>119013610</v>
       </c>
       <c r="B61" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555196</v>
+        <v>554901</v>
       </c>
       <c r="R61" t="n">
-        <v>6954028</v>
+        <v>6953841</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7086,12 +6883,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>21 bladrosetter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,6 +6902,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7118,50 +6921,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119013555</v>
+        <v>119013611</v>
       </c>
       <c r="B62" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555253</v>
+        <v>554915</v>
       </c>
       <c r="R62" t="n">
-        <v>6953747</v>
+        <v>6953952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7188,12 +6990,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,6 +7009,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7220,50 +7028,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119013553</v>
+        <v>119013612</v>
       </c>
       <c r="B63" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>554843</v>
+        <v>554911</v>
       </c>
       <c r="R63" t="n">
-        <v>6953762</v>
+        <v>6953840</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7290,12 +7097,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>18 bladrosetter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7304,6 +7116,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7322,15 +7135,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119013585</v>
+        <v>119013549</v>
       </c>
       <c r="B64" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7338,21 +7146,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7362,10 +7170,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555009</v>
+        <v>555196</v>
       </c>
       <c r="R64" t="n">
-        <v>6953842</v>
+        <v>6954028</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,12 +7200,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7424,15 +7232,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119013550</v>
+        <v>119013552</v>
       </c>
       <c r="B65" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7464,10 +7267,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555259</v>
+        <v>555115</v>
       </c>
       <c r="R65" t="n">
-        <v>6953737</v>
+        <v>6954152</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7526,15 +7329,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119013587</v>
+        <v>119013599</v>
       </c>
       <c r="B66" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7542,21 +7340,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7566,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555104</v>
+        <v>554908</v>
       </c>
       <c r="R66" t="n">
-        <v>6953849</v>
+        <v>6953845</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7628,54 +7426,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119013581</v>
+        <v>119013523</v>
       </c>
       <c r="B67" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555306</v>
+        <v>555402</v>
       </c>
       <c r="R67" t="n">
-        <v>6954137</v>
+        <v>6954240</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7702,17 +7491,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>200 bladrosetter 8 blomställningar</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7721,7 +7505,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7740,15 +7523,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119013532</v>
+        <v>119013525</v>
       </c>
       <c r="B68" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7780,10 +7558,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555251</v>
+        <v>555195</v>
       </c>
       <c r="R68" t="n">
-        <v>6953766</v>
+        <v>6953833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,54 +7620,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119013610</v>
+        <v>119013526</v>
       </c>
       <c r="B69" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>554901</v>
+        <v>555407</v>
       </c>
       <c r="R69" t="n">
-        <v>6953841</v>
+        <v>6954244</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7916,17 +7685,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>21 bladrosetter</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7935,7 +7699,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7954,54 +7717,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119013608</v>
+        <v>119013529</v>
       </c>
       <c r="B70" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555081</v>
+        <v>555390</v>
       </c>
       <c r="R70" t="n">
-        <v>6953860</v>
+        <v>6954230</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8028,17 +7782,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>200 bladrosetter 11 blomställningar</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8047,7 +7796,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8066,15 +7814,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119013589</v>
+        <v>119013530</v>
       </c>
       <c r="B71" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8106,10 +7849,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555079</v>
+        <v>555091</v>
       </c>
       <c r="R71" t="n">
-        <v>6954055</v>
+        <v>6954136</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8136,12 +7879,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8168,15 +7911,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119013545</v>
+        <v>119013531</v>
       </c>
       <c r="B72" t="n">
-        <v>97794</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8184,21 +7922,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8208,10 +7946,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555395</v>
+        <v>554814</v>
       </c>
       <c r="R72" t="n">
-        <v>6954240</v>
+        <v>6954160</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8270,15 +8008,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119013576</v>
+        <v>119013533</v>
       </c>
       <c r="B73" t="n">
-        <v>97793</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8286,21 +8019,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8310,10 +8043,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>554812</v>
+        <v>555383</v>
       </c>
       <c r="R73" t="n">
-        <v>6954136</v>
+        <v>6954209</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8372,15 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119013531</v>
+        <v>119013537</v>
       </c>
       <c r="B74" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8412,10 +8140,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>554814</v>
+        <v>554955</v>
       </c>
       <c r="R74" t="n">
-        <v>6954160</v>
+        <v>6954151</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8474,37 +8202,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119013541</v>
+        <v>119013538</v>
       </c>
       <c r="B75" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8514,10 +8237,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>555060</v>
+        <v>555196</v>
       </c>
       <c r="R75" t="n">
-        <v>6954137</v>
+        <v>6954028</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,54 +8299,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119013607</v>
+        <v>119013585</v>
       </c>
       <c r="B76" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555004</v>
+        <v>555009</v>
       </c>
       <c r="R76" t="n">
-        <v>6953947</v>
+        <v>6953842</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8658,18 +8372,12 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>500 bladrosetter 20 blomställningar</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8688,37 +8396,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119013540</v>
+        <v>119013586</v>
       </c>
       <c r="B77" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8728,10 +8431,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>554986</v>
+        <v>554909</v>
       </c>
       <c r="R77" t="n">
-        <v>6954151</v>
+        <v>6954096</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,12 +8461,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8790,15 +8493,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119013527</v>
+        <v>119013587</v>
       </c>
       <c r="B78" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8830,10 +8528,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>554830</v>
+        <v>555104</v>
       </c>
       <c r="R78" t="n">
-        <v>6953771</v>
+        <v>6953849</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8860,12 +8558,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8892,74 +8590,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119013583</v>
+        <v>119013588</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555004</v>
+        <v>555102</v>
       </c>
       <c r="R79" t="n">
-        <v>6953949</v>
+        <v>6954018</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9018,58 +8687,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124801658</v>
+        <v>119013589</v>
       </c>
       <c r="B80" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>554914</v>
+        <v>555079</v>
       </c>
       <c r="R80" t="n">
-        <v>6954151</v>
+        <v>6954055</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9093,22 +8752,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9123,70 +8772,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124801653</v>
+        <v>119013590</v>
       </c>
       <c r="B81" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>554970</v>
+        <v>555064</v>
       </c>
       <c r="R81" t="n">
-        <v>6954058</v>
+        <v>6953871</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9210,27 +8849,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>06:20</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>färska barkfläk</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9245,27 +8869,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124801657</v>
+        <v>119013593</v>
       </c>
       <c r="B82" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9273,42 +8892,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>554914</v>
+        <v>554896</v>
       </c>
       <c r="R82" t="n">
-        <v>6954151</v>
+        <v>6953861</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9332,22 +8946,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9362,27 +8966,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124801651</v>
+        <v>119013594</v>
       </c>
       <c r="B83" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9390,46 +8989,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103031</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>554989</v>
+        <v>554818</v>
       </c>
       <c r="R83" t="n">
-        <v>6954003</v>
+        <v>6954164</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9453,22 +9043,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>06:50</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>06:50</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9483,27 +9063,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124801644</v>
+        <v>119013543</v>
       </c>
       <c r="B84" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9511,42 +9086,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>223591</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555209</v>
+        <v>554949</v>
       </c>
       <c r="R84" t="n">
-        <v>6953983</v>
+        <v>6954156</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9570,12 +9140,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9590,70 +9160,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124801648</v>
+        <v>119013545</v>
       </c>
       <c r="B85" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99036</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>223591</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555153</v>
+        <v>555395</v>
       </c>
       <c r="R85" t="n">
-        <v>6954003</v>
+        <v>6954240</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9677,17 +9237,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>många färska bark</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9702,69 +9257,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124801645</v>
+        <v>119013546</v>
       </c>
       <c r="B86" t="n">
-        <v>57884</v>
+        <v>99036</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>lokmyrhöjden, Jmt</t>
+          <t>Eltnäs, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>554946</v>
+        <v>555203</v>
       </c>
       <c r="R86" t="n">
-        <v>6953955</v>
+        <v>6954010</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9788,22 +9334,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9818,15 +9354,808 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>119013547</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>555032</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6954136</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>119013548</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>554814</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6954160</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>119013595</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>554913</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6954097</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>119013596</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>555083</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6954043</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>119013597</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>554986</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6954063</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>119013598</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>555001</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6953846</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>96790283</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lokmyrhöjdens västsida, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>555216</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6953887</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>tät, drygt 100-årig barrskog</t>
+        </is>
+      </c>
+      <c r="AN93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>2 substratenheter # äldre sälg</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>119013606</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Eltnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>554958</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6953843</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43131-2023 artfynd.xlsx
+++ b/artfynd/A 43131-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790280</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790274</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790269</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013613</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013614</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790268</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790285</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790286</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013554</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013555</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013601</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013602</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2246,6 +2321,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013603</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013604</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2440,6 +2525,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013584</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2537,6 +2627,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013540</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2634,6 +2729,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013541</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013542</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2852,6 +2957,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013583</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2968,6 +3078,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801645</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3075,6 +3190,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801648</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3192,6 +3312,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801653</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3294,6 +3419,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801644</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3406,6 +3536,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801657</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3503,6 +3638,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013521</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3615,6 +3755,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801658</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3731,6 +3876,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124801651</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3828,6 +3978,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013575</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3925,6 +4080,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013576</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4022,6 +4182,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013577</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4119,6 +4284,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013578</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4216,6 +4386,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013579</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4322,6 +4497,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790277</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4419,6 +4599,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013558</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4516,6 +4701,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013559</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4613,6 +4803,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013560</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4710,6 +4905,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013561</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4824,6 +5024,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790278</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4938,6 +5143,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790281</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5052,6 +5262,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790282</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5159,6 +5374,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013562</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5261,6 +5481,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013563</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5368,6 +5593,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013565</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5475,6 +5705,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013566</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5582,6 +5817,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013568</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5684,6 +5924,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013570</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5791,6 +6036,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013571</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5898,6 +6148,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013573</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6005,6 +6260,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013581</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6112,6 +6372,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013607</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6219,6 +6484,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013608</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6326,6 +6596,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013609</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6433,6 +6708,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013610</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6540,6 +6820,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013611</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6647,6 +6932,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013612</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6744,6 +7034,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013549</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6841,6 +7136,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013550</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6938,6 +7238,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013552</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7035,6 +7340,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013553</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7132,6 +7442,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013599</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7229,6 +7544,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013523</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7326,6 +7646,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013524</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7423,6 +7748,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013525</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7520,6 +7850,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013526</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7617,6 +7952,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013527</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7714,6 +8054,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013529</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7811,6 +8156,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013530</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7908,6 +8258,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013531</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8005,6 +8360,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013532</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8102,6 +8462,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013533</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8199,6 +8564,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013537</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8296,6 +8666,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013538</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8393,6 +8768,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013585</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8490,6 +8870,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013586</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8587,6 +8972,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013587</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8684,6 +9074,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013588</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8781,6 +9176,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013589</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8878,6 +9278,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013590</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8975,6 +9380,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013593</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9072,6 +9482,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013594</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9169,6 +9584,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013543</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9266,6 +9686,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013545</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9363,6 +9788,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013546</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9460,6 +9890,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013547</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9557,6 +9992,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013548</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9654,6 +10094,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013595</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9751,6 +10196,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013596</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9848,6 +10298,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013597</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9945,6 +10400,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013598</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10059,6 +10519,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790283</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10156,8 +10621,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013606</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>